--- a/Final_Submission_Deliverables/2_Excel_Nextute_Case_B_Financial_Model.xlsx
+++ b/Final_Submission_Deliverables/2_Excel_Nextute_Case_B_Financial_Model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\AppData\Roaming\Microsoft\Windows\Network Shortcuts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68A26F8B-6F0F-4D1C-8F09-7C8235D93CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39F5D549-BC41-4096-8A0B-4C155E99DABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
